--- a/templates/usa_expense_report_template.xlsx
+++ b/templates/usa_expense_report_template.xlsx
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="J1" s="12" t="n">
-        <v>6.8</v>
+        <v>6.8175</v>
       </c>
     </row>
     <row r="2">
